--- a/src/prediction/test_eval_results.xlsx
+++ b/src/prediction/test_eval_results.xlsx
@@ -486,22 +486,22 @@
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6513203978538513</v>
+        <v>0.6239594221115112</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3486796021461487</v>
+        <v>0.3760405778884888</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1513203978538513</v>
+        <v>0.1239594221115112</v>
       </c>
       <c r="G2" t="b">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6513203978538513</v>
+        <v>0.6239594221115112</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3486796021461487</v>
+        <v>0.3760405778884888</v>
       </c>
     </row>
   </sheetData>
